--- a/cet4/result/64_音乐女神_爵士女王的传奇/64_音乐女神_爵士女王的传奇_学习版.xlsx
+++ b/cet4/result/64_音乐女神_爵士女王的传奇/64_音乐女神_爵士女王的传奇_学习版.xlsx
@@ -397,745 +397,563 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D39"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>jazz</v>
       </c>
       <c r="B2" t="str">
-        <v>jazz</v>
+        <v>/dʒæz/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>爵士乐</v>
       </c>
-      <c r="D2" t="str">
-        <v>jazz(爵士乐)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>nineteen</v>
       </c>
       <c r="B3" t="str">
-        <v>nineteen</v>
+        <v>/ˌnaɪnˈtiːn/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./num.</v>
+      </c>
+      <c r="D3" t="str">
         <v>十九</v>
       </c>
-      <c r="D3" t="str">
-        <v>nineteen(十九)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>sister</v>
       </c>
       <c r="B4" t="str">
-        <v>sister</v>
+        <v>/ˈsɪstər/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>姐妹</v>
       </c>
-      <c r="D4" t="str">
-        <v>sister(姐妹)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>worry</v>
       </c>
       <c r="B5" t="str">
-        <v>worry</v>
+        <v>/ˈwɜːri/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D5" t="str">
         <v>担心</v>
       </c>
-      <c r="D5" t="str">
-        <v>worry(担心)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>intend</v>
       </c>
       <c r="B6" t="str">
-        <v>intend</v>
+        <v>/ɪnˈtend/</v>
       </c>
       <c r="C6" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>打算</v>
       </c>
-      <c r="D6" t="str">
-        <v>intend(打算)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>properly</v>
       </c>
       <c r="B7" t="str">
-        <v>properly</v>
+        <v>/ˈprɑːpərli/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D7" t="str">
         <v>适当地</v>
       </c>
-      <c r="D7" t="str">
-        <v>properly(适当地)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>miner</v>
       </c>
       <c r="B8" t="str">
-        <v>miner</v>
+        <v>/ˈmaɪnər/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>矿工</v>
       </c>
-      <c r="D8" t="str">
-        <v>miner(矿工)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>widow</v>
       </c>
       <c r="B9" t="str">
-        <v>widow</v>
+        <v>/ˈwɪdoʊ/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D9" t="str">
         <v>寡妇</v>
       </c>
-      <c r="D9" t="str">
-        <v>widow(寡妇)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>iron</v>
       </c>
       <c r="B10" t="str">
-        <v>iron</v>
+        <v>/ˈaɪərn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>铁</v>
       </c>
-      <c r="D10" t="str">
-        <v>iron(铁)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>powerful</v>
       </c>
       <c r="B11" t="str">
-        <v>powerful</v>
+        <v>/ˈpaʊərfl/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D11" t="str">
         <v>强大的</v>
       </c>
-      <c r="D11" t="str">
-        <v>powerful(强大的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>bitterly</v>
       </c>
       <c r="B12" t="str">
-        <v>bitterly</v>
+        <v>/ˈbɪtərli/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D12" t="str">
         <v>苦涩地</v>
       </c>
-      <c r="D12" t="str">
-        <v>bitterly(苦涩地)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>invite</v>
       </c>
       <c r="B13" t="str">
-        <v>invite</v>
+        <v>/ɪnˈvaɪt/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D13" t="str">
         <v>邀请</v>
       </c>
-      <c r="D13" t="str">
-        <v>invite(邀请)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>refresh</v>
       </c>
       <c r="B14" t="str">
-        <v>sister</v>
+        <v>/rɪˈfreʃ/</v>
       </c>
       <c r="C14" t="str">
-        <v>姐妹</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D14" t="str">
-        <v>sister(姐妹)📢</v>
+        <v>更新</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>feather</v>
       </c>
       <c r="B15" t="str">
-        <v>refresh</v>
+        <v>/ˈfeðər/</v>
       </c>
       <c r="C15" t="str">
-        <v>更新</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D15" t="str">
-        <v>refresh(更新)📢</v>
+        <v>羽毛</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>smell</v>
       </c>
       <c r="B16" t="str">
-        <v>feather</v>
+        <v>/smel/</v>
       </c>
       <c r="C16" t="str">
-        <v>羽毛</v>
+        <v>n./v.</v>
       </c>
       <c r="D16" t="str">
-        <v>feather(羽毛)📢</v>
+        <v>气味</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>plantation</v>
       </c>
       <c r="B17" t="str">
-        <v>smell</v>
+        <v>/plænˈteɪʃn/</v>
       </c>
       <c r="C17" t="str">
-        <v>气味</v>
+        <v>n./adj.</v>
       </c>
       <c r="D17" t="str">
-        <v>smell(气味)📢</v>
+        <v>种植园</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>injure</v>
       </c>
       <c r="B18" t="str">
-        <v>plantation</v>
+        <v>/ˈɪndʒər/</v>
       </c>
       <c r="C18" t="str">
-        <v>种植园</v>
+        <v>vt.</v>
       </c>
       <c r="D18" t="str">
-        <v>plantation(种植园)📢</v>
+        <v>伤害</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>sock</v>
       </c>
       <c r="B19" t="str">
-        <v>injure</v>
+        <v>/sɑːk/</v>
       </c>
       <c r="C19" t="str">
-        <v>伤害</v>
+        <v>n./vt./v./adj./adv.</v>
       </c>
       <c r="D19" t="str">
-        <v>injure(伤害)📢</v>
+        <v>袜</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>tower</v>
       </c>
       <c r="B20" t="str">
-        <v>sock</v>
+        <v>/ˈtaʊər/</v>
       </c>
       <c r="C20" t="str">
-        <v>袜</v>
+        <v>n./vi.</v>
       </c>
       <c r="D20" t="str">
-        <v>sock(袜)📢</v>
+        <v>塔</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>bright</v>
       </c>
       <c r="B21" t="str">
-        <v>tower</v>
+        <v>/braɪt/</v>
       </c>
       <c r="C21" t="str">
-        <v>塔</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D21" t="str">
-        <v>tower(塔)📢</v>
+        <v>明亮的</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>significance</v>
       </c>
       <c r="B22" t="str">
-        <v>sister</v>
+        <v>/sɪɡˈnɪfɪkəns/</v>
       </c>
       <c r="C22" t="str">
-        <v>姐妹</v>
+        <v>n.</v>
       </c>
       <c r="D22" t="str">
-        <v>sister(姐妹)📢</v>
+        <v>意义</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>example</v>
       </c>
       <c r="B23" t="str">
-        <v>bright</v>
+        <v>/ɪɡˈzæmpl/</v>
       </c>
       <c r="C23" t="str">
-        <v>明亮的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D23" t="str">
-        <v>bright(明亮的)📢</v>
+        <v>榜样</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>contain</v>
       </c>
       <c r="B24" t="str">
-        <v>significance</v>
+        <v>/kənˈteɪn/</v>
       </c>
       <c r="C24" t="str">
-        <v>意义</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D24" t="str">
-        <v>significance(意义)📢</v>
+        <v>包含</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>manufacturer</v>
       </c>
       <c r="B25" t="str">
-        <v>example</v>
+        <v>/ˌmænjuˈfæktʃərər/</v>
       </c>
       <c r="C25" t="str">
-        <v>榜样</v>
+        <v>n.</v>
       </c>
       <c r="D25" t="str">
-        <v>example(榜样)📢</v>
+        <v>制造商</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>flu</v>
       </c>
       <c r="B26" t="str">
-        <v>contain</v>
+        <v>/fluː/</v>
       </c>
       <c r="C26" t="str">
-        <v>包含</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>contain(包含)📢</v>
+        <v>流感</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>remember</v>
       </c>
       <c r="B27" t="str">
-        <v>invite</v>
+        <v>/rɪˈmembər/</v>
       </c>
       <c r="C27" t="str">
-        <v>邀请</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>invite(邀请)📢</v>
+        <v>记得</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>canvas</v>
       </c>
       <c r="B28" t="str">
-        <v>manufacturer</v>
+        <v>/ˈkænvəs/</v>
       </c>
       <c r="C28" t="str">
-        <v>制造商</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>manufacturer(制造商)📢</v>
+        <v>帆布</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>urgent</v>
       </c>
       <c r="B29" t="str">
-        <v>flu</v>
+        <v>/ˈɜːrdʒənt/</v>
       </c>
       <c r="C29" t="str">
-        <v>流感</v>
+        <v>adj.</v>
       </c>
       <c r="D29" t="str">
-        <v>flu(流感)📢</v>
+        <v>紧急的</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>automobile</v>
       </c>
       <c r="B30" t="str">
-        <v>remember</v>
+        <v>/ˈɔːtəməbiːl/</v>
       </c>
       <c r="C30" t="str">
-        <v>记得</v>
+        <v>n./vt.</v>
       </c>
       <c r="D30" t="str">
-        <v>remember(记得)📢</v>
+        <v>汽车</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>that</v>
       </c>
       <c r="B31" t="str">
-        <v>canvas</v>
+        <v>/ðæt/</v>
       </c>
       <c r="C31" t="str">
-        <v>帆布</v>
+        <v>n./adj./pron./conj.</v>
       </c>
       <c r="D31" t="str">
-        <v>canvas(帆布)📢</v>
+        <v>那个</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>accent</v>
       </c>
       <c r="B32" t="str">
-        <v>sister</v>
+        <v>/ˈæksənt/</v>
       </c>
       <c r="C32" t="str">
-        <v>姐妹</v>
+        <v>n./vt.</v>
       </c>
       <c r="D32" t="str">
-        <v>sister(姐妹)📢</v>
+        <v>口音</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>content</v>
       </c>
       <c r="B33" t="str">
-        <v>urgent</v>
+        <v>/'kɑntent/</v>
       </c>
       <c r="C33" t="str">
-        <v>紧急的</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>urgent(紧急的)📢</v>
+        <v>内容</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>team</v>
       </c>
       <c r="B34" t="str">
-        <v>invite</v>
+        <v>/tiːm/</v>
       </c>
       <c r="C34" t="str">
-        <v>邀请</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>invite(邀请)📢</v>
+        <v>团队</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>wax</v>
       </c>
       <c r="B35" t="str">
-        <v>automobile</v>
+        <v>/wæks/</v>
       </c>
       <c r="C35" t="str">
-        <v>汽车</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>automobile(汽车)📢</v>
+        <v>蜡</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>grateful</v>
       </c>
       <c r="B36" t="str">
-        <v>that</v>
+        <v>/ˈɡreɪtfl/</v>
       </c>
       <c r="C36" t="str">
-        <v>那个</v>
+        <v>adj.</v>
       </c>
       <c r="D36" t="str">
-        <v>that(那个)📢</v>
+        <v>感谢的</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>thousand</v>
       </c>
       <c r="B37" t="str">
-        <v>accent</v>
+        <v>/ˈθaʊznd/</v>
       </c>
       <c r="C37" t="str">
-        <v>口音</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>accent(口音)📢</v>
+        <v>一千</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>childish</v>
       </c>
       <c r="B38" t="str">
-        <v>content</v>
+        <v>/ˈtʃaɪldɪʃ/</v>
       </c>
       <c r="C38" t="str">
-        <v>内容</v>
+        <v>adj.</v>
       </c>
       <c r="D38" t="str">
-        <v>content(内容)📢</v>
+        <v>幼稚的</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>lazy</v>
       </c>
       <c r="B39" t="str">
-        <v>team</v>
+        <v>/ˈleɪzi/</v>
       </c>
       <c r="C39" t="str">
-        <v>团队</v>
+        <v>n./adj.</v>
       </c>
       <c r="D39" t="str">
-        <v>team(团队)📢</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>wax</v>
-      </c>
-      <c r="C40" t="str">
-        <v>蜡</v>
-      </c>
-      <c r="D40" t="str">
-        <v>wax(蜡)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>accent</v>
-      </c>
-      <c r="C41" t="str">
-        <v>口音</v>
-      </c>
-      <c r="D41" t="str">
-        <v>accent(口音)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>grateful</v>
-      </c>
-      <c r="C42" t="str">
-        <v>感谢的</v>
-      </c>
-      <c r="D42" t="str">
-        <v>grateful(感谢的)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>thousand</v>
-      </c>
-      <c r="C43" t="str">
-        <v>一千</v>
-      </c>
-      <c r="D43" t="str">
-        <v>thousand(一千)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>invite</v>
-      </c>
-      <c r="C44" t="str">
-        <v>邀请</v>
-      </c>
-      <c r="D44" t="str">
-        <v>invite(邀请)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>automobile</v>
-      </c>
-      <c r="C45" t="str">
-        <v>汽车</v>
-      </c>
-      <c r="D45" t="str">
-        <v>automobile(汽车)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>canvas</v>
-      </c>
-      <c r="C46" t="str">
-        <v>帆布</v>
-      </c>
-      <c r="D46" t="str">
-        <v>canvas(帆布)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>bright</v>
-      </c>
-      <c r="C47" t="str">
-        <v>明亮的</v>
-      </c>
-      <c r="D47" t="str">
-        <v>bright(明亮的)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>childish</v>
-      </c>
-      <c r="C48" t="str">
-        <v>幼稚的</v>
-      </c>
-      <c r="D48" t="str">
-        <v>childish(幼稚的)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>manufacturer</v>
-      </c>
-      <c r="C49" t="str">
-        <v>制造商</v>
-      </c>
-      <c r="D49" t="str">
-        <v>manufacturer(制造商)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>lazy</v>
-      </c>
-      <c r="C50" t="str">
         <v>懒惰的</v>
-      </c>
-      <c r="D50" t="str">
-        <v>lazy(懒惰的)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>sister</v>
-      </c>
-      <c r="C51" t="str">
-        <v>姐妹</v>
-      </c>
-      <c r="D51" t="str">
-        <v>sister(姐妹)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>feather</v>
-      </c>
-      <c r="C52" t="str">
-        <v>羽毛</v>
-      </c>
-      <c r="D52" t="str">
-        <v>feather(羽毛)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
   </ignoredErrors>
 </worksheet>
 </file>